--- a/Outcome/Appendix/Tables/New_robustness_operational_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_robustness_operational_summaries.xlsx
@@ -963,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0.740898804489451</v>
@@ -1433,13 +1433,13 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="G16" t="n">
-        <v>0.372</v>
+        <v>0.298</v>
       </c>
       <c r="H16" t="n">
-        <v>0.375</v>
+        <v>0.447</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2153,35 +2153,29 @@
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
         <v>68</v>
       </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>71</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
       <c r="N5" t="s">
         <v>5</v>
       </c>
@@ -2757,34 +2751,34 @@
         <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="E16" t="n">
-        <v>0.372</v>
+        <v>0.298</v>
       </c>
       <c r="F16" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G16" t="n">
-        <v>0.375</v>
+        <v>0.447</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -3534,35 +3528,29 @@
         <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
         <v>68</v>
       </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>71</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
       <c r="N5" t="s">
         <v>5</v>
       </c>
@@ -4138,34 +4126,34 @@
         <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="E16" t="n">
-        <v>0.372</v>
+        <v>0.298</v>
       </c>
       <c r="F16" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G16" t="n">
-        <v>0.375</v>
+        <v>0.447</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -4960,35 +4948,31 @@
         <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K5"/>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>55</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="P5"/>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -5001,9 +4985,7 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -5663,34 +5645,34 @@
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="H16" t="n">
-        <v>0.372</v>
+        <v>0.298</v>
       </c>
       <c r="I16" t="n">
-        <v>0.375</v>
+        <v>0.447</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
       </c>
       <c r="M16" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="N16" t="n">
-        <v>0.372</v>
+        <v>0.298</v>
       </c>
       <c r="O16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -7722,7 +7704,7 @@
         <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>95</v>
@@ -7731,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -7948,7 +7930,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
         <v>98</v>
@@ -7960,13 +7942,13 @@
         <v>95</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
         <v>24</v>
@@ -8086,7 +8068,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
@@ -8097,7 +8079,7 @@
         <v>104</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -8108,7 +8090,7 @@
         <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>

--- a/Outcome/Appendix/Tables/New_robustness_operational_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_robustness_operational_summaries.xlsx
@@ -315,13 +315,13 @@
     <t xml:space="preserve">Bayesian structural</t>
   </si>
   <si>
+    <t xml:space="preserve">TBATS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Neural Network</t>
   </si>
   <si>
     <t xml:space="preserve">SARIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBATS</t>
   </si>
   <si>
     <t xml:space="preserve">AlternativeRule</t>
@@ -403,7 +403,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -440,7 +442,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,13 +1129,13 @@
         <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="G9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="H9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1341,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -1382,22 +1384,22 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
         <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="G15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="H15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1433,13 +1435,13 @@
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="G16" t="n">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="H16" t="n">
-        <v>0.447</v>
+        <v>0.364</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1519,13 +1521,13 @@
         <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="I18" t="n">
         <v>-5</v>
@@ -1598,28 +1600,28 @@
         <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>0.852</v>
+        <v>0.429</v>
       </c>
       <c r="G20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="I20" t="n">
         <v>-2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K20" t="n">
         <v>1.02186511965192</v>
@@ -1686,22 +1688,22 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>0.997</v>
+        <v>0.956</v>
       </c>
       <c r="G22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="H22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
@@ -2359,16 +2361,16 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="F9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="G9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -2660,13 +2662,13 @@
         <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L14" t="n">
         <v>32</v>
       </c>
       <c r="M14" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
         <v>5</v>
@@ -2695,34 +2697,34 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="E15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N15" t="s">
         <v>5</v>
@@ -2751,34 +2753,34 @@
         <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="E16" t="n">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="F16" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.447</v>
+        <v>0.364</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>67</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
         <v>68</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>69</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -2828,13 +2830,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17" t="n">
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N17" t="s">
         <v>5</v>
@@ -2863,7 +2865,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2872,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="H18" t="n">
         <v>47</v>
       </c>
       <c r="I18" t="n">
-        <v>0.150000000000006</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>61</v>
@@ -2969,34 +2971,34 @@
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>0.852</v>
+        <v>0.429</v>
       </c>
       <c r="E20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.062</v>
+        <v>0.338</v>
       </c>
       <c r="G20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L20" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="M20" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N20" t="s">
         <v>5</v>
@@ -3081,34 +3083,34 @@
         <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>0.997</v>
+        <v>0.956</v>
       </c>
       <c r="E22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="F22" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="G22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="H22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K22" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N22" t="s">
         <v>5</v>
@@ -3734,16 +3736,16 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="F9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="G9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -4035,13 +4037,13 @@
         <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L14" t="n">
         <v>32</v>
       </c>
       <c r="M14" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
         <v>5</v>
@@ -4070,34 +4072,34 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="E15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N15" t="s">
         <v>5</v>
@@ -4126,34 +4128,34 @@
         <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="E16" t="n">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="F16" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.447</v>
+        <v>0.364</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>67</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
         <v>68</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>69</v>
       </c>
       <c r="N16" t="s">
         <v>5</v>
@@ -4203,13 +4205,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17" t="n">
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N17" t="s">
         <v>5</v>
@@ -4238,7 +4240,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4247,13 +4249,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="H18" t="n">
         <v>47</v>
       </c>
       <c r="I18" t="n">
-        <v>0.150000000000006</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>61</v>
@@ -4344,34 +4346,34 @@
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>0.852</v>
+        <v>0.429</v>
       </c>
       <c r="E20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.062</v>
+        <v>0.338</v>
       </c>
       <c r="G20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L20" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="M20" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N20" t="s">
         <v>5</v>
@@ -4456,34 +4458,34 @@
         <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>0.997</v>
+        <v>0.956</v>
       </c>
       <c r="E22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="F22" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="G22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="H22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K22" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N22" t="s">
         <v>5</v>
@@ -5190,13 +5192,13 @@
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="H9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -5208,10 +5210,10 @@
         <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="N9" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -5527,7 +5529,7 @@
         <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -5542,7 +5544,7 @@
         <v>9</v>
       </c>
       <c r="P14" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -5580,34 +5582,34 @@
         <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="H15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="I15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="J15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
       </c>
       <c r="M15" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="N15" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -5645,34 +5647,34 @@
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="H16" t="n">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="I16" t="n">
-        <v>0.447</v>
+        <v>0.364</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
       </c>
       <c r="M16" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="N16" t="n">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -5722,7 +5724,7 @@
         <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
@@ -5737,7 +5739,7 @@
         <v>31</v>
       </c>
       <c r="P17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -5775,13 +5777,13 @@
         <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="J18" t="n">
         <v>47</v>
@@ -5791,7 +5793,7 @@
         <v>26</v>
       </c>
       <c r="M18" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5899,34 +5901,34 @@
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.852</v>
+        <v>0.429</v>
       </c>
       <c r="H20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
       </c>
       <c r="M20" t="n">
-        <v>0.852</v>
+        <v>0.429</v>
       </c>
       <c r="N20" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="O20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P20" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -6029,34 +6031,34 @@
         <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.997</v>
+        <v>0.956</v>
       </c>
       <c r="H22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="I22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="J22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
       </c>
       <c r="M22" t="n">
-        <v>0.997</v>
+        <v>0.956</v>
       </c>
       <c r="N22" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="O22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P22" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -6819,7 +6821,7 @@
         <v>44105</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>44805</v>
@@ -6851,22 +6853,22 @@
         <v>22</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44075</v>
+        <v>43983</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44075</v>
+        <v>43983</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>45017</v>
+        <v>44896</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -7044,22 +7046,22 @@
         <v>22</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44927</v>
+        <v>44197</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>45474</v>
+        <v>45047</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>45505</v>
+        <v>45108</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>45505</v>
+        <v>45139</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -7126,22 +7128,22 @@
         <v>22</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -7443,7 +7445,7 @@
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
@@ -7452,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -7469,7 +7471,7 @@
         <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>95</v>
@@ -7478,7 +7480,7 @@
         <v>95</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -7495,16 +7497,16 @@
         <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -7524,7 +7526,7 @@
         <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
         <v>95</v>
@@ -7533,7 +7535,7 @@
         <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -7588,7 +7590,7 @@
         <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
@@ -7640,25 +7642,25 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>43</v>
@@ -7704,7 +7706,7 @@
         <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
         <v>95</v>
@@ -7713,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -7788,19 +7790,19 @@
         <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -7820,7 +7822,7 @@
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -7843,16 +7845,16 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -7881,7 +7883,7 @@
         <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -7890,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="s">
         <v>24</v>
@@ -7901,16 +7903,16 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -7933,7 +7935,7 @@
         <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>94</v>
@@ -7959,16 +7961,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -7994,7 +7996,7 @@
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
         <v>95</v>
@@ -8003,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -8017,19 +8019,19 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -8068,7 +8070,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
@@ -8079,7 +8081,7 @@
         <v>104</v>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -8090,7 +8092,7 @@
         <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
